--- a/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
+++ b/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pending" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI29"/>
+  <dimension ref="A1:AI22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>202609191300</t>
+          <t>202609210300</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>20260822</t>
+          <t>20260817</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-08-22, Return : 2026-08-23</t>
+          <t>Pickup : 2026-08-17, Return : 2026-08-18</t>
         </is>
       </c>
       <c r="O3" s="4" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>202609230700</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -902,7 +902,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx10 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -944,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R4" s="4" t="n">
         <v>0</v>
@@ -1014,22 +1014,22 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260701964</t>
+          <t>HASLS22260800573</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>0151N</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>202609230700</t>
+          <t>202609200100</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -1040,53 +1040,53 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
+          <t>TRUE MARINE CO., LTD.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>INOAC (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYURETHANE FOAM</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>**REQUEST GOOD AND CLEAN CONTAINER**</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>CY-RTN : 09-13/09/2026 (PR2610001634)
-** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER **</t>
+          <t>Pickup : 2026-09-05, Return : 2026-09-07 // FM SWSR 2610N BY HAL DD.07/09
+(1ST RETURN 14/09 W/O RENT)</t>
         </is>
       </c>
       <c r="O5" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="4" t="n">
         <v>0</v>
@@ -1156,22 +1156,22 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260800573</t>
+          <t>HASLS22260801481</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>0151N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>202609192000</t>
+          <t>202609232100</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -1182,53 +1182,53 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>20260905</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>TRUE MARINE CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>INOAC (THAILAND) CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>POLYURETHANE FOAM</t>
+          <t xml:space="preserve">POLYAMIDE RESIN </t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>**REQUEST GOOD AND CLEAN CONTAINER**</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-05, Return : 2026-09-07 // FM SWSR 2610N BY HAL DD.07/09
-(1ST RETURN 14/09 W/O RENT)</t>
+          <t>CY-RTN :04-05/09/2026
+**CHANGED FM VSL."KMSU 2606S" BY K.HATAIPACH DD.20/8/26**</t>
         </is>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260800855</t>
+          <t>HASLS22260801601</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>0151N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>202609192000</t>
+          <t>202609212300</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -1324,43 +1324,44 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx5 </t>
+          <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>SAMSUNG SDS GLOBAL SCL (THAILAND) CO.,LTD.</t>
+          <t>DYNAMIC INTERTRANSPORT CO., LTD.</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
+          <t>CP-MEIJI CO., LTD.</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>REFRIGERATOR</t>
+          <t>FRESH MILK AND MILK PRODUCT</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>*No containers with cut and patch marks inside*
-GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
+          <t>(Temp +0.0℃ / Vent Close) 
+REQUEST : CLEAN AND GOOD CONTAINER FOR MILK PRODUCT</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-07, Return : 2026-09-12</t>
+          <t>Pickup : 2026-09-12, Return : 2026-09-13 (Temp +0.0 / Vent Close) 
+CLS TIME 14/09/26 @18.00</t>
         </is>
       </c>
       <c r="O7" s="4" t="n">
@@ -1370,13 +1371,13 @@
         <v>0</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0</v>
@@ -1440,22 +1441,22 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801481</t>
+          <t>HASLS22260801603</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>202609222100</t>
+          <t>202609212300</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -1466,59 +1467,60 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>DYNAMIC INTERTRANSPORT CO., LTD.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>CP-MEIJI CO., LTD.</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">POLYAMIDE RESIN </t>
+          <t>FRESH MILK AND MILK PRODUCT</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>(Temp +0.0℃ / Vent Close)  
+REQUEST : CLEAN AND GOOD CONTAINER FOR MILK PRODUCT</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>CY-RTN :04-05/09/2026
-**CHANGED FM VSL."KMSU 2606S" BY K.HATAIPACH DD.20/8/26**</t>
+          <t>Pickup : 2026-09-12, Return : 2026-09-13  (Temp +0.0 / Vent Close) 
+CLS TIME 14/09/26 @18.00</t>
         </is>
       </c>
       <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>0</v>
@@ -1597,7 +1599,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>202609211500</t>
+          <t>202609212300</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -1739,7 +1741,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>202609211500</t>
+          <t>202609212300</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -1881,7 +1883,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>202609211500</t>
+          <t>202609212300</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2023,7 +2025,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>202609242200</t>
+          <t>202609250800</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2165,7 +2167,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>202609242200</t>
+          <t>202609250800</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2307,7 +2309,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>202609242200</t>
+          <t>202609250800</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2434,22 +2436,22 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801873</t>
+          <t>HASLS22260802565</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>202609150600</t>
+          <t>202609232100</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2460,48 +2462,47 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>JPTMK</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">R40Hx1 </t>
+          <t xml:space="preserve">20'x6 </t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>LOGMAN INTERNATIONAL CO., LTD.</t>
+          <t>IRPC PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>THAI NIPPON FOODS CO. , LTD.</t>
+          <t>IRPC PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>FROZEN CHICKEN</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>(Temp -20.0℃ / Vent Close) 
-REQ: NEW AND CLEAN CONTAINER</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>[FIX]Pickup : 2026-09-07, Return : 2026-09-10 (Temp -20.0 / Vent Close) 
-CLS TIME 11/09/26 @18.0</t>
+          <t>CY - RTN : 09-11/09/2026
+*PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER*</t>
         </is>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>0</v>
@@ -2513,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0</v>
@@ -2577,22 +2578,22 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802371</t>
+          <t>HASLS22260900006</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>202609150600</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2603,53 +2604,53 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>JPHSM</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>L.A.1 CO.,LTD.</t>
+          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>CHEMICALS PRODUCT DG CARGO</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>**APPROVE DG BY CYS33 DD: 01/09/26** MIX DG22GPx1 (CLS 9 / UN 3082, CLS 8 / UN 3265)</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>**APPROVE DG BY CYS33 DD: 01/09/26** MIX DG22GPx1 (CLS 9 / UN 3082, CLS 8 / UN 3265) 
-Pickup : 2026-09-03, Return @JWD : 2026-09-04</t>
+          <t>CY-RTN 09-13/09/26 
+*PLS CHECK OPEN GATE BEFORE RETURN CTNR*</t>
         </is>
       </c>
       <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="P16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="R16" s="4" t="n">
         <v>0</v>
@@ -2719,22 +2720,22 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802467</t>
+          <t>HASLS22260900026</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>0151N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>202609192000</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2745,53 +2746,53 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx7 </t>
+          <t xml:space="preserve">20'x4 </t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>SAMSUNG SDS GLOBAL SCL (THAILAND) CO.,LTD.</t>
+          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>WASHING MATCHINE</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>*No containers with cut and patch marks inside*
-GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-07, Return : 2026-09-12</t>
+          <t>CY-RTN : 09-13/09/2026 (PR2610002068)
+** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER **</t>
         </is>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R17" s="4" t="n">
         <v>0</v>
@@ -2861,22 +2862,22 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802468</t>
+          <t>HASLS22260900118</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>0151N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>202609192000</t>
+          <t>202609232100</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2887,43 +2888,42 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20RFx1 </t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>SAMSUNG SDS GLOBAL SCL (THAILAND) CO.,LTD.</t>
+          <t>FM GLOBAL LOGISTICS CO., LTD.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
+          <t>CCL LABEL (THAI) LTD.</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>DISH WASHER</t>
+          <t>PRINTED LABEL</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>*No containers with cut and patch marks inside*
-GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
+          <t>(Temp +20.0℃ / Vent 20% Open): We require a container of this shipment that is dry, clean, and free from any water.</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-07, Return : 2026-09-12</t>
+          <t xml:space="preserve">Pickup : 2026-09-10, Return : 2026-09-10 RF22REx1 (Temp +20.0 / Vent 20% Open) </t>
         </is>
       </c>
       <c r="O18" s="4" t="n">
@@ -2933,10 +2933,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="4" t="n">
         <v>0</v>
@@ -3003,22 +3003,22 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802565</t>
+          <t>HASLS22260900358</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>202609222100</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x6 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -3044,32 +3044,32 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>IRPC PUBLIC COMPANY LIMITED</t>
+          <t>WORLDLINK SHIPPING CO., LTD.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>IRPC PUBLIC COMPANY LIMITED</t>
+          <t>QUAKER HOUGHTON (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>LUBRICANT</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQUEST CONTAINER GRADE  A OR B</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>CY - RTN : 09-11/09/2026
-*PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER*</t>
+          <t>Pickup : 2026-09-09, Return : 2026-09-10 (1ST RTN DD: 19/09/26 WO/RENT)
+**CHECK OPENGATE BEFORE RETURN CNTR**</t>
         </is>
       </c>
       <c r="O19" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>0</v>
@@ -3145,12 +3145,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900006</t>
+          <t>HASLS22260900623</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>202609230700</t>
+          <t>202609212300</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -3171,53 +3171,53 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>JPHSM</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
+          <t>MORRISON EXPRESS CORP (THAILAND)LTD.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>WESTERN DIGITAL STORAGE TECHNOLOGIES (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>BOXBLUE BOX</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>CY-RTN 09-13/09/26 
-*PLS CHECK OPEN GATE BEFORE RETURN CTNR*</t>
+          <t xml:space="preserve">Pickup : 2026-09-12, Return : 2026-09-14 (1ST RTN 15/09 W/O RENT) 
+ </t>
         </is>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" s="4" t="n">
         <v>0</v>
@@ -3287,7 +3287,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900018</t>
+          <t>HASLS22260900925</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>202609230700</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -3313,12 +3313,12 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>JPIYM</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx6 </t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -3348,18 +3348,19 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>CY-RTN 09-13/09/26 
-*PLS CHECK OPEN GATE BEFORE RETURN CTNR*</t>
+          <t xml:space="preserve">CY-RTN : 09-13/09/2026
+*PLS CHECK OPEN GATE BEFORE RETURN CTNR*
+</t>
         </is>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R21" s="4" t="n">
         <v>0</v>
@@ -3427,1100 +3428,108 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900026</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>SWIC</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>202609230700</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x4 </t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CTNR</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>CY-RTN : 09-13/09/2026 (PR2610002068)
-** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER **</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="4">
-        <f>SUM(O22:W22)-X22</f>
-        <v/>
-      </c>
-      <c r="AA22" s="4">
-        <f>MAX(0,O22-MAX(0,X22))</f>
-        <v/>
-      </c>
-      <c r="AB22" s="4">
-        <f>MAX(0,P22-MAX(0,X22-SUM(O22:O22)))</f>
-        <v/>
-      </c>
-      <c r="AC22" s="4">
-        <f>MAX(0,Q22-MAX(0,X22-SUM(O22:P22)))</f>
-        <v/>
-      </c>
-      <c r="AD22" s="4">
-        <f>MAX(0,R22-MAX(0,X22-SUM(O22:Q22)))</f>
-        <v/>
-      </c>
-      <c r="AE22" s="4">
-        <f>MAX(0,S22-MAX(0,X22-SUM(O22:R22)))</f>
-        <v/>
-      </c>
-      <c r="AF22" s="4">
-        <f>MAX(0,T22-MAX(0,X22-SUM(O22:S22)))</f>
-        <v/>
-      </c>
-      <c r="AG22" s="4">
-        <f>MAX(0,U22-MAX(0,X22-SUM(O22:T22)))</f>
-        <v/>
-      </c>
-      <c r="AH22" s="4">
-        <f>MAX(0,V22-MAX(0,X22-SUM(O22:U22)))</f>
-        <v/>
-      </c>
-      <c r="AI22" s="4">
-        <f>MAX(0,W22-MAX(0,X22-SUM(O22:V22)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900027</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>SWIC</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>202609230700</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CTNR</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>CY-RTN : 09-13/09/2026 
-** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER **</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="4">
-        <f>SUM(O23:W23)-X23</f>
-        <v/>
-      </c>
-      <c r="AA23" s="4">
-        <f>MAX(0,O23-MAX(0,X23))</f>
-        <v/>
-      </c>
-      <c r="AB23" s="4">
-        <f>MAX(0,P23-MAX(0,X23-SUM(O23:O23)))</f>
-        <v/>
-      </c>
-      <c r="AC23" s="4">
-        <f>MAX(0,Q23-MAX(0,X23-SUM(O23:P23)))</f>
-        <v/>
-      </c>
-      <c r="AD23" s="4">
-        <f>MAX(0,R23-MAX(0,X23-SUM(O23:Q23)))</f>
-        <v/>
-      </c>
-      <c r="AE23" s="4">
-        <f>MAX(0,S23-MAX(0,X23-SUM(O23:R23)))</f>
-        <v/>
-      </c>
-      <c r="AF23" s="4">
-        <f>MAX(0,T23-MAX(0,X23-SUM(O23:S23)))</f>
-        <v/>
-      </c>
-      <c r="AG23" s="4">
-        <f>MAX(0,U23-MAX(0,X23-SUM(O23:T23)))</f>
-        <v/>
-      </c>
-      <c r="AH23" s="4">
-        <f>MAX(0,V23-MAX(0,X23-SUM(O23:U23)))</f>
-        <v/>
-      </c>
-      <c r="AI23" s="4">
-        <f>MAX(0,W23-MAX(0,X23-SUM(O23:V23)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900062</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>SWSR</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>202609172200</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>RHENUS LOGISTICS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>UMC ELECTRONICS (THAILAND) LTD.</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>PCBA (8537.20.29)</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>good and clean container</t>
-        </is>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-09, Return : 2026-09-10</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="4">
-        <f>SUM(O24:W24)-X24</f>
-        <v/>
-      </c>
-      <c r="AA24" s="4">
-        <f>MAX(0,O24-MAX(0,X24))</f>
-        <v/>
-      </c>
-      <c r="AB24" s="4">
-        <f>MAX(0,P24-MAX(0,X24-SUM(O24:O24)))</f>
-        <v/>
-      </c>
-      <c r="AC24" s="4">
-        <f>MAX(0,Q24-MAX(0,X24-SUM(O24:P24)))</f>
-        <v/>
-      </c>
-      <c r="AD24" s="4">
-        <f>MAX(0,R24-MAX(0,X24-SUM(O24:Q24)))</f>
-        <v/>
-      </c>
-      <c r="AE24" s="4">
-        <f>MAX(0,S24-MAX(0,X24-SUM(O24:R24)))</f>
-        <v/>
-      </c>
-      <c r="AF24" s="4">
-        <f>MAX(0,T24-MAX(0,X24-SUM(O24:S24)))</f>
-        <v/>
-      </c>
-      <c r="AG24" s="4">
-        <f>MAX(0,U24-MAX(0,X24-SUM(O24:T24)))</f>
-        <v/>
-      </c>
-      <c r="AH24" s="4">
-        <f>MAX(0,V24-MAX(0,X24-SUM(O24:U24)))</f>
-        <v/>
-      </c>
-      <c r="AI24" s="4">
-        <f>MAX(0,W24-MAX(0,X24-SUM(O24:V24)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900160</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>202609150600</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx10 </t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>BRIDGESTONE INDUSTRIAL PRODUCTS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>AIR CONDITIONING HOSE</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>GOOD DRY AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-11 </t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="R25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="4">
-        <f>SUM(O25:W25)-X25</f>
-        <v/>
-      </c>
-      <c r="AA25" s="4">
-        <f>MAX(0,O25-MAX(0,X25))</f>
-        <v/>
-      </c>
-      <c r="AB25" s="4">
-        <f>MAX(0,P25-MAX(0,X25-SUM(O25:O25)))</f>
-        <v/>
-      </c>
-      <c r="AC25" s="4">
-        <f>MAX(0,Q25-MAX(0,X25-SUM(O25:P25)))</f>
-        <v/>
-      </c>
-      <c r="AD25" s="4">
-        <f>MAX(0,R25-MAX(0,X25-SUM(O25:Q25)))</f>
-        <v/>
-      </c>
-      <c r="AE25" s="4">
-        <f>MAX(0,S25-MAX(0,X25-SUM(O25:R25)))</f>
-        <v/>
-      </c>
-      <c r="AF25" s="4">
-        <f>MAX(0,T25-MAX(0,X25-SUM(O25:S25)))</f>
-        <v/>
-      </c>
-      <c r="AG25" s="4">
-        <f>MAX(0,U25-MAX(0,X25-SUM(O25:T25)))</f>
-        <v/>
-      </c>
-      <c r="AH25" s="4">
-        <f>MAX(0,V25-MAX(0,X25-SUM(O25:U25)))</f>
-        <v/>
-      </c>
-      <c r="AI25" s="4">
-        <f>MAX(0,W25-MAX(0,X25-SUM(O25:V25)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900305</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>202609150600</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>JPTYO</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>20260903</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CTNR</t>
-        </is>
-      </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>CY-RTN 03-05/09/26 
-*PLS CHECK OPEN GATE BEFORE RETURN CTNR*</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="4">
-        <f>SUM(O26:W26)-X26</f>
-        <v/>
-      </c>
-      <c r="AA26" s="4">
-        <f>MAX(0,O26-MAX(0,X26))</f>
-        <v/>
-      </c>
-      <c r="AB26" s="4">
-        <f>MAX(0,P26-MAX(0,X26-SUM(O26:O26)))</f>
-        <v/>
-      </c>
-      <c r="AC26" s="4">
-        <f>MAX(0,Q26-MAX(0,X26-SUM(O26:P26)))</f>
-        <v/>
-      </c>
-      <c r="AD26" s="4">
-        <f>MAX(0,R26-MAX(0,X26-SUM(O26:Q26)))</f>
-        <v/>
-      </c>
-      <c r="AE26" s="4">
-        <f>MAX(0,S26-MAX(0,X26-SUM(O26:R26)))</f>
-        <v/>
-      </c>
-      <c r="AF26" s="4">
-        <f>MAX(0,T26-MAX(0,X26-SUM(O26:S26)))</f>
-        <v/>
-      </c>
-      <c r="AG26" s="4">
-        <f>MAX(0,U26-MAX(0,X26-SUM(O26:T26)))</f>
-        <v/>
-      </c>
-      <c r="AH26" s="4">
-        <f>MAX(0,V26-MAX(0,X26-SUM(O26:U26)))</f>
-        <v/>
-      </c>
-      <c r="AI26" s="4">
-        <f>MAX(0,W26-MAX(0,X26-SUM(O26:V26)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900358</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>SWIC</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>202609230700</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>WORLDLINK SHIPPING CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>QUAKER HOUGHTON (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>LUBRICANT</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>REQUEST CONTAINER GRADE  A OR B</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-09, Return : 2026-09-10 (1ST RTN DD: 19/09/26 WO/RENT)
-**CHECK OPENGATE BEFORE RETURN CNTR**</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="4">
-        <f>SUM(O27:W27)-X27</f>
-        <v/>
-      </c>
-      <c r="AA27" s="4">
-        <f>MAX(0,O27-MAX(0,X27))</f>
-        <v/>
-      </c>
-      <c r="AB27" s="4">
-        <f>MAX(0,P27-MAX(0,X27-SUM(O27:O27)))</f>
-        <v/>
-      </c>
-      <c r="AC27" s="4">
-        <f>MAX(0,Q27-MAX(0,X27-SUM(O27:P27)))</f>
-        <v/>
-      </c>
-      <c r="AD27" s="4">
-        <f>MAX(0,R27-MAX(0,X27-SUM(O27:Q27)))</f>
-        <v/>
-      </c>
-      <c r="AE27" s="4">
-        <f>MAX(0,S27-MAX(0,X27-SUM(O27:R27)))</f>
-        <v/>
-      </c>
-      <c r="AF27" s="4">
-        <f>MAX(0,T27-MAX(0,X27-SUM(O27:S27)))</f>
-        <v/>
-      </c>
-      <c r="AG27" s="4">
-        <f>MAX(0,U27-MAX(0,X27-SUM(O27:T27)))</f>
-        <v/>
-      </c>
-      <c r="AH27" s="4">
-        <f>MAX(0,V27-MAX(0,X27-SUM(O27:U27)))</f>
-        <v/>
-      </c>
-      <c r="AI27" s="4">
-        <f>MAX(0,W27-MAX(0,X27-SUM(O27:V27)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900490</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>DJCF</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>0151N</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>202609192000</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x2 </t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>PHOENIX TRANS LOGISTICS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>GROWELL ABRASIVES (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>STEEL SHOT</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-09, Return : 2026-09-10 (1ST RTN DD: 14/09/26 WO/RENT)
-**CHECK OPENGATE BEFORE RETURN CNTR**</t>
-        </is>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="4">
-        <f>SUM(O28:W28)-X28</f>
-        <v/>
-      </c>
-      <c r="AA28" s="4">
-        <f>MAX(0,O28-MAX(0,X28))</f>
-        <v/>
-      </c>
-      <c r="AB28" s="4">
-        <f>MAX(0,P28-MAX(0,X28-SUM(O28:O28)))</f>
-        <v/>
-      </c>
-      <c r="AC28" s="4">
-        <f>MAX(0,Q28-MAX(0,X28-SUM(O28:P28)))</f>
-        <v/>
-      </c>
-      <c r="AD28" s="4">
-        <f>MAX(0,R28-MAX(0,X28-SUM(O28:Q28)))</f>
-        <v/>
-      </c>
-      <c r="AE28" s="4">
-        <f>MAX(0,S28-MAX(0,X28-SUM(O28:R28)))</f>
-        <v/>
-      </c>
-      <c r="AF28" s="4">
-        <f>MAX(0,T28-MAX(0,X28-SUM(O28:S28)))</f>
-        <v/>
-      </c>
-      <c r="AG28" s="4">
-        <f>MAX(0,U28-MAX(0,X28-SUM(O28:T28)))</f>
-        <v/>
-      </c>
-      <c r="AH28" s="4">
-        <f>MAX(0,V28-MAX(0,X28-SUM(O28:U28)))</f>
-        <v/>
-      </c>
-      <c r="AI28" s="4">
-        <f>MAX(0,W28-MAX(0,X28-SUM(O28:V28)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5">
-        <f>SUM(O3:O28)</f>
-        <v/>
-      </c>
-      <c r="P29" s="5">
-        <f>SUM(P3:P28)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="5">
-        <f>SUM(Q3:Q28)</f>
-        <v/>
-      </c>
-      <c r="R29" s="5">
-        <f>SUM(R3:R28)</f>
-        <v/>
-      </c>
-      <c r="S29" s="5">
-        <f>SUM(S3:S28)</f>
-        <v/>
-      </c>
-      <c r="T29" s="5">
-        <f>SUM(T3:T28)</f>
-        <v/>
-      </c>
-      <c r="U29" s="5">
-        <f>SUM(U3:U28)</f>
-        <v/>
-      </c>
-      <c r="V29" s="5">
-        <f>SUM(V3:V28)</f>
-        <v/>
-      </c>
-      <c r="W29" s="5">
-        <f>SUM(W3:W28)</f>
-        <v/>
-      </c>
-      <c r="X29" s="5">
-        <f>SUM(X3:X28)</f>
-        <v/>
-      </c>
-      <c r="Y29" s="5" t="n"/>
-      <c r="Z29" s="5">
-        <f>SUM(Z3:Z28)</f>
-        <v/>
-      </c>
-      <c r="AA29" s="5">
-        <f>SUM(AA3:AA28)</f>
-        <v/>
-      </c>
-      <c r="AB29" s="5">
-        <f>SUM(AB3:AB28)</f>
-        <v/>
-      </c>
-      <c r="AC29" s="5">
-        <f>SUM(AC3:AC28)</f>
-        <v/>
-      </c>
-      <c r="AD29" s="5">
-        <f>SUM(AD3:AD28)</f>
-        <v/>
-      </c>
-      <c r="AE29" s="5">
-        <f>SUM(AE3:AE28)</f>
-        <v/>
-      </c>
-      <c r="AF29" s="5">
-        <f>SUM(AF3:AF28)</f>
-        <v/>
-      </c>
-      <c r="AG29" s="5">
-        <f>SUM(AG3:AG28)</f>
-        <v/>
-      </c>
-      <c r="AH29" s="5">
-        <f>SUM(AH3:AH28)</f>
-        <v/>
-      </c>
-      <c r="AI29" s="5">
-        <f>SUM(AI3:AI28)</f>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5">
+        <f>SUM(O3:O21)</f>
+        <v/>
+      </c>
+      <c r="P22" s="5">
+        <f>SUM(P3:P21)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="5">
+        <f>SUM(Q3:Q21)</f>
+        <v/>
+      </c>
+      <c r="R22" s="5">
+        <f>SUM(R3:R21)</f>
+        <v/>
+      </c>
+      <c r="S22" s="5">
+        <f>SUM(S3:S21)</f>
+        <v/>
+      </c>
+      <c r="T22" s="5">
+        <f>SUM(T3:T21)</f>
+        <v/>
+      </c>
+      <c r="U22" s="5">
+        <f>SUM(U3:U21)</f>
+        <v/>
+      </c>
+      <c r="V22" s="5">
+        <f>SUM(V3:V21)</f>
+        <v/>
+      </c>
+      <c r="W22" s="5">
+        <f>SUM(W3:W21)</f>
+        <v/>
+      </c>
+      <c r="X22" s="5">
+        <f>SUM(X3:X21)</f>
+        <v/>
+      </c>
+      <c r="Y22" s="5" t="n"/>
+      <c r="Z22" s="5">
+        <f>SUM(Z3:Z21)</f>
+        <v/>
+      </c>
+      <c r="AA22" s="5">
+        <f>SUM(AA3:AA21)</f>
+        <v/>
+      </c>
+      <c r="AB22" s="5">
+        <f>SUM(AB3:AB21)</f>
+        <v/>
+      </c>
+      <c r="AC22" s="5">
+        <f>SUM(AC3:AC21)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="5">
+        <f>SUM(AD3:AD21)</f>
+        <v/>
+      </c>
+      <c r="AE22" s="5">
+        <f>SUM(AE3:AE21)</f>
+        <v/>
+      </c>
+      <c r="AF22" s="5">
+        <f>SUM(AF3:AF21)</f>
+        <v/>
+      </c>
+      <c r="AG22" s="5">
+        <f>SUM(AG3:AG21)</f>
+        <v/>
+      </c>
+      <c r="AH22" s="5">
+        <f>SUM(AH3:AH21)</f>
+        <v/>
+      </c>
+      <c r="AI22" s="5">
+        <f>SUM(AI3:AI21)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AI28"/>
+  <autoFilter ref="A2:AI21"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AI1"/>
   </mergeCells>

--- a/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
+++ b/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AG$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AG$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG30"/>
+  <dimension ref="A1:AG25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -731,25 +731,25 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260700701</t>
+          <t>HASLS22260701405</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>ICVY</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>202609210500</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -757,32 +757,32 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>20260817</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>CHEMICALS PRODUCT (NON DG)</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>REQUEST :  CONTAINER MAX GROSS 32.50 TONS</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P3" s="4" t="n">
         <v>0</v>
@@ -862,25 +862,25 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260701405</t>
+          <t>HASLS22260801614</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>ICVY</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>202609220200</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n"/>
+          <t>202609211900</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -888,42 +888,42 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>INGREDION (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>MODIFIED TAPIOCA STARCH (GRADE : PURITY 21T)</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>0</v>
@@ -991,263 +991,263 @@
       </c>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260800573</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>DJCF</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>0151N</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>202609201300</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>HASLS22260801673</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>202609231400</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>20260905</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>INOAC (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>POLYURETHANE FOAM</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>**REQUEST GOOD AND CLEAN CONTAINER**</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>POSTMAN (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>FRESH COCONUT</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="4">
+      <c r="R5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="5">
         <f>SUM(M5:U5)-V5</f>
         <v/>
       </c>
-      <c r="Y5" s="4">
+      <c r="Y5" s="5">
         <f>MAX(0,M5-MAX(0,V5))</f>
         <v/>
       </c>
-      <c r="Z5" s="4">
+      <c r="Z5" s="5">
         <f>MAX(0,N5-MAX(0,V5-SUM(M5:M5)))</f>
         <v/>
       </c>
-      <c r="AA5" s="4">
+      <c r="AA5" s="5">
         <f>MAX(0,O5-MAX(0,V5-SUM(M5:N5)))</f>
         <v/>
       </c>
-      <c r="AB5" s="4">
+      <c r="AB5" s="5">
         <f>MAX(0,P5-MAX(0,V5-SUM(M5:O5)))</f>
         <v/>
       </c>
-      <c r="AC5" s="4">
+      <c r="AC5" s="5">
         <f>MAX(0,Q5-MAX(0,V5-SUM(M5:P5)))</f>
         <v/>
       </c>
-      <c r="AD5" s="4">
+      <c r="AD5" s="5">
         <f>MAX(0,R5-MAX(0,V5-SUM(M5:Q5)))</f>
         <v/>
       </c>
-      <c r="AE5" s="4">
+      <c r="AE5" s="5">
         <f>MAX(0,S5-MAX(0,V5-SUM(M5:R5)))</f>
         <v/>
       </c>
-      <c r="AF5" s="4">
+      <c r="AF5" s="5">
         <f>MAX(0,T5-MAX(0,V5-SUM(M5:S5)))</f>
         <v/>
       </c>
-      <c r="AG5" s="4">
+      <c r="AG5" s="5">
         <f>MAX(0,U5-MAX(0,V5-SUM(M5:T5)))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260801481</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>2607S</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>HASLS22260801674</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>202609231400</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>20260904</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POLYAMIDE RESIN </t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="n">
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>POSTMAN (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>FRESH COCONUT</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="4">
+      <c r="R6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="5">
         <f>SUM(M6:U6)-V6</f>
         <v/>
       </c>
-      <c r="Y6" s="4">
+      <c r="Y6" s="5">
         <f>MAX(0,M6-MAX(0,V6))</f>
         <v/>
       </c>
-      <c r="Z6" s="4">
+      <c r="Z6" s="5">
         <f>MAX(0,N6-MAX(0,V6-SUM(M6:M6)))</f>
         <v/>
       </c>
-      <c r="AA6" s="4">
+      <c r="AA6" s="5">
         <f>MAX(0,O6-MAX(0,V6-SUM(M6:N6)))</f>
         <v/>
       </c>
-      <c r="AB6" s="4">
+      <c r="AB6" s="5">
         <f>MAX(0,P6-MAX(0,V6-SUM(M6:O6)))</f>
         <v/>
       </c>
-      <c r="AC6" s="4">
+      <c r="AC6" s="5">
         <f>MAX(0,Q6-MAX(0,V6-SUM(M6:P6)))</f>
         <v/>
       </c>
-      <c r="AD6" s="4">
+      <c r="AD6" s="5">
         <f>MAX(0,R6-MAX(0,V6-SUM(M6:Q6)))</f>
         <v/>
       </c>
-      <c r="AE6" s="4">
+      <c r="AE6" s="5">
         <f>MAX(0,S6-MAX(0,V6-SUM(M6:R6)))</f>
         <v/>
       </c>
-      <c r="AF6" s="4">
+      <c r="AF6" s="5">
         <f>MAX(0,T6-MAX(0,V6-SUM(M6:S6)))</f>
         <v/>
       </c>
-      <c r="AG6" s="4">
+      <c r="AG6" s="5">
         <f>MAX(0,U6-MAX(0,V6-SUM(M6:T6)))</f>
         <v/>
       </c>
@@ -1255,7 +1255,7 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>HASLS22260801601</t>
+          <t>HASLS22260801675</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1270,10 +1270,10 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>202609230100</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n"/>
+          <t>202609231400</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -1291,23 +1291,22 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>20260912</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>CP-MEIJI CO., LTD.</t>
+          <t>POSTMAN (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>FRESH MILK AND MILK PRODUCT</t>
+          <t>FRESH COCONUT</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>(Temp +0.0℃ / Vent Close) 
-REQUEST : CLEAN AND GOOD CONTAINER FOR MILK PRODUCT</t>
+          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
         </is>
       </c>
       <c r="M7" s="5" t="n">
@@ -1387,25 +1386,25 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>HASLS22260801673</t>
+          <t>HASLS22260801677</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>202609230100</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n"/>
+          <t>202609250500</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1423,7 +1422,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>20260905</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -1518,25 +1517,25 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>HASLS22260801674</t>
+          <t>HASLS22260801679</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>202609230100</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n"/>
+          <t>202609250500</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1554,7 +1553,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>20260905</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1649,25 +1648,25 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>HASLS22260801675</t>
+          <t>HASLS22260801681</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>202609230100</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n"/>
+          <t>202609250500</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
       <c r="F10" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1685,7 +1684,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>20260905</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1780,25 +1779,25 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>HASLS22260801677</t>
+          <t>HASLS22260801684</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>202609250500</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n"/>
+          <t>202610041300</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1816,7 +1815,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1911,25 +1910,25 @@
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>HASLS22260801679</t>
+          <t>HASLS22260801685</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>202609250500</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n"/>
+          <t>202610041300</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1947,7 +1946,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -2040,1721 +2039,1066 @@
       </c>
     </row>
     <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260801681</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>202609250500</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900107</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>HAB</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>202610250630</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>FRESH COCONUT</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="5">
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x10 </t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>EIAM THONGCHAI INDUSTRY CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>STARCH</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>REQ : FOOD GRADE CONTAINER CLEAR &amp;DRY NO OIL NO RUSTY</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="4">
         <f>SUM(M13:U13)-V13</f>
         <v/>
       </c>
-      <c r="Y13" s="5">
+      <c r="Y13" s="4">
         <f>MAX(0,M13-MAX(0,V13))</f>
         <v/>
       </c>
-      <c r="Z13" s="5">
+      <c r="Z13" s="4">
         <f>MAX(0,N13-MAX(0,V13-SUM(M13:M13)))</f>
         <v/>
       </c>
-      <c r="AA13" s="5">
+      <c r="AA13" s="4">
         <f>MAX(0,O13-MAX(0,V13-SUM(M13:N13)))</f>
         <v/>
       </c>
-      <c r="AB13" s="5">
+      <c r="AB13" s="4">
         <f>MAX(0,P13-MAX(0,V13-SUM(M13:O13)))</f>
         <v/>
       </c>
-      <c r="AC13" s="5">
+      <c r="AC13" s="4">
         <f>MAX(0,Q13-MAX(0,V13-SUM(M13:P13)))</f>
         <v/>
       </c>
-      <c r="AD13" s="5">
+      <c r="AD13" s="4">
         <f>MAX(0,R13-MAX(0,V13-SUM(M13:Q13)))</f>
         <v/>
       </c>
-      <c r="AE13" s="5">
+      <c r="AE13" s="4">
         <f>MAX(0,S13-MAX(0,V13-SUM(M13:R13)))</f>
         <v/>
       </c>
-      <c r="AF13" s="5">
+      <c r="AF13" s="4">
         <f>MAX(0,T13-MAX(0,V13-SUM(M13:S13)))</f>
         <v/>
       </c>
-      <c r="AG13" s="5">
+      <c r="AG13" s="4">
         <f>MAX(0,U13-MAX(0,V13-SUM(M13:T13)))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260801684</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>SWAT</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>202610041300</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900237</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2607S</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>202609220800</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>20260914</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>FRESH COCONUT</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5" t="n">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>ECOLAB LIMITED</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>QUATERNARY AMMONIUM COMPOUND DRM</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>APPROVAL BY Mr.LEE MINHA DD.07/09/2026 (CLS 8 / UN 2920) Request good and clean container</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="5">
+      <c r="P14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="4">
         <f>SUM(M14:U14)-V14</f>
         <v/>
       </c>
-      <c r="Y14" s="5">
+      <c r="Y14" s="4">
         <f>MAX(0,M14-MAX(0,V14))</f>
         <v/>
       </c>
-      <c r="Z14" s="5">
+      <c r="Z14" s="4">
         <f>MAX(0,N14-MAX(0,V14-SUM(M14:M14)))</f>
         <v/>
       </c>
-      <c r="AA14" s="5">
+      <c r="AA14" s="4">
         <f>MAX(0,O14-MAX(0,V14-SUM(M14:N14)))</f>
         <v/>
       </c>
-      <c r="AB14" s="5">
+      <c r="AB14" s="4">
         <f>MAX(0,P14-MAX(0,V14-SUM(M14:O14)))</f>
         <v/>
       </c>
-      <c r="AC14" s="5">
+      <c r="AC14" s="4">
         <f>MAX(0,Q14-MAX(0,V14-SUM(M14:P14)))</f>
         <v/>
       </c>
-      <c r="AD14" s="5">
+      <c r="AD14" s="4">
         <f>MAX(0,R14-MAX(0,V14-SUM(M14:Q14)))</f>
         <v/>
       </c>
-      <c r="AE14" s="5">
+      <c r="AE14" s="4">
         <f>MAX(0,S14-MAX(0,V14-SUM(M14:R14)))</f>
         <v/>
       </c>
-      <c r="AF14" s="5">
+      <c r="AF14" s="4">
         <f>MAX(0,T14-MAX(0,V14-SUM(M14:S14)))</f>
         <v/>
       </c>
-      <c r="AG14" s="5">
+      <c r="AG14" s="4">
         <f>MAX(0,U14-MAX(0,V14-SUM(M14:T14)))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260801685</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>SWAT</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>202610041300</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900238</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2607S</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>202609220800</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>20260914</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>FRESH COCONUT</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5" t="n">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>ECOLAB LIMITED</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>FLOOR CLEANER</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>Request good and clean container</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="5">
+      <c r="P15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="4">
         <f>SUM(M15:U15)-V15</f>
         <v/>
       </c>
-      <c r="Y15" s="5">
+      <c r="Y15" s="4">
         <f>MAX(0,M15-MAX(0,V15))</f>
         <v/>
       </c>
-      <c r="Z15" s="5">
+      <c r="Z15" s="4">
         <f>MAX(0,N15-MAX(0,V15-SUM(M15:M15)))</f>
         <v/>
       </c>
-      <c r="AA15" s="5">
+      <c r="AA15" s="4">
         <f>MAX(0,O15-MAX(0,V15-SUM(M15:N15)))</f>
         <v/>
       </c>
-      <c r="AB15" s="5">
+      <c r="AB15" s="4">
         <f>MAX(0,P15-MAX(0,V15-SUM(M15:O15)))</f>
         <v/>
       </c>
-      <c r="AC15" s="5">
+      <c r="AC15" s="4">
         <f>MAX(0,Q15-MAX(0,V15-SUM(M15:P15)))</f>
         <v/>
       </c>
-      <c r="AD15" s="5">
+      <c r="AD15" s="4">
         <f>MAX(0,R15-MAX(0,V15-SUM(M15:Q15)))</f>
         <v/>
       </c>
-      <c r="AE15" s="5">
+      <c r="AE15" s="4">
         <f>MAX(0,S15-MAX(0,V15-SUM(M15:R15)))</f>
         <v/>
       </c>
-      <c r="AF15" s="5">
+      <c r="AF15" s="4">
         <f>MAX(0,T15-MAX(0,V15-SUM(M15:S15)))</f>
         <v/>
       </c>
-      <c r="AG15" s="5">
+      <c r="AG15" s="4">
         <f>MAX(0,U15-MAX(0,V15-SUM(M15:T15)))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260801686</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>SWAT</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900623</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>202610041300</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>202609231400</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>FRESH COCONUT</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="5" t="n">
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>WESTERN DIGITAL STORAGE TECHNOLOGIES (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>BOXBLUE BOX</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="5">
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4">
         <f>SUM(M16:U16)-V16</f>
         <v/>
       </c>
-      <c r="Y16" s="5">
+      <c r="Y16" s="4">
         <f>MAX(0,M16-MAX(0,V16))</f>
         <v/>
       </c>
-      <c r="Z16" s="5">
+      <c r="Z16" s="4">
         <f>MAX(0,N16-MAX(0,V16-SUM(M16:M16)))</f>
         <v/>
       </c>
-      <c r="AA16" s="5">
+      <c r="AA16" s="4">
         <f>MAX(0,O16-MAX(0,V16-SUM(M16:N16)))</f>
         <v/>
       </c>
-      <c r="AB16" s="5">
+      <c r="AB16" s="4">
         <f>MAX(0,P16-MAX(0,V16-SUM(M16:O16)))</f>
         <v/>
       </c>
-      <c r="AC16" s="5">
+      <c r="AC16" s="4">
         <f>MAX(0,Q16-MAX(0,V16-SUM(M16:P16)))</f>
         <v/>
       </c>
-      <c r="AD16" s="5">
+      <c r="AD16" s="4">
         <f>MAX(0,R16-MAX(0,V16-SUM(M16:Q16)))</f>
         <v/>
       </c>
-      <c r="AE16" s="5">
+      <c r="AE16" s="4">
         <f>MAX(0,S16-MAX(0,V16-SUM(M16:R16)))</f>
         <v/>
       </c>
-      <c r="AF16" s="5">
+      <c r="AF16" s="4">
         <f>MAX(0,T16-MAX(0,V16-SUM(M16:S16)))</f>
         <v/>
       </c>
-      <c r="AG16" s="5">
+      <c r="AG16" s="4">
         <f>MAX(0,U16-MAX(0,V16-SUM(M16:T16)))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900107</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>HAB</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>202610251430</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>HASLS22260900952</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>202609271030</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x10 </t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>EIAM THONGCHAI INDUSTRY CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>STARCH</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>REQ : FOOD GRADE CONTAINER CLEAR &amp;DRY NO OIL NO RUSTY</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="4">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>POSTMAN (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>RF45REx1 (Temp +2.0℃ / Vent 15% Open)</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="5">
         <f>SUM(M17:U17)-V17</f>
         <v/>
       </c>
-      <c r="Y17" s="4">
+      <c r="Y17" s="5">
         <f>MAX(0,M17-MAX(0,V17))</f>
         <v/>
       </c>
-      <c r="Z17" s="4">
+      <c r="Z17" s="5">
         <f>MAX(0,N17-MAX(0,V17-SUM(M17:M17)))</f>
         <v/>
       </c>
-      <c r="AA17" s="4">
+      <c r="AA17" s="5">
         <f>MAX(0,O17-MAX(0,V17-SUM(M17:N17)))</f>
         <v/>
       </c>
-      <c r="AB17" s="4">
+      <c r="AB17" s="5">
         <f>MAX(0,P17-MAX(0,V17-SUM(M17:O17)))</f>
         <v/>
       </c>
-      <c r="AC17" s="4">
+      <c r="AC17" s="5">
         <f>MAX(0,Q17-MAX(0,V17-SUM(M17:P17)))</f>
         <v/>
       </c>
-      <c r="AD17" s="4">
+      <c r="AD17" s="5">
         <f>MAX(0,R17-MAX(0,V17-SUM(M17:Q17)))</f>
         <v/>
       </c>
-      <c r="AE17" s="4">
+      <c r="AE17" s="5">
         <f>MAX(0,S17-MAX(0,V17-SUM(M17:R17)))</f>
         <v/>
       </c>
-      <c r="AF17" s="4">
+      <c r="AF17" s="5">
         <f>MAX(0,T17-MAX(0,V17-SUM(M17:S17)))</f>
         <v/>
       </c>
-      <c r="AG17" s="4">
+      <c r="AG17" s="5">
         <f>MAX(0,U17-MAX(0,V17-SUM(M17:T17)))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900237</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>HASLS22260901033</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>KMSU</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>2607S</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>202609271100</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>ECOLAB LIMITED</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>QUATERNARY AMMONIUM COMPOUND DRM</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>APPROVAL BY Mr.LEE MINHA DD.07/09/2026 (CLS 8 / UN 2920) Request good and clean container</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="4" t="n">
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>INTER FRESH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>(Temp +2.0℃ / Vent 30% Open) Request for new container and We don't accept STAR COOL brand reefer containers.</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="4">
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="5">
         <f>SUM(M18:U18)-V18</f>
         <v/>
       </c>
-      <c r="Y18" s="4">
+      <c r="Y18" s="5">
         <f>MAX(0,M18-MAX(0,V18))</f>
         <v/>
       </c>
-      <c r="Z18" s="4">
+      <c r="Z18" s="5">
         <f>MAX(0,N18-MAX(0,V18-SUM(M18:M18)))</f>
         <v/>
       </c>
-      <c r="AA18" s="4">
+      <c r="AA18" s="5">
         <f>MAX(0,O18-MAX(0,V18-SUM(M18:N18)))</f>
         <v/>
       </c>
-      <c r="AB18" s="4">
+      <c r="AB18" s="5">
         <f>MAX(0,P18-MAX(0,V18-SUM(M18:O18)))</f>
         <v/>
       </c>
-      <c r="AC18" s="4">
+      <c r="AC18" s="5">
         <f>MAX(0,Q18-MAX(0,V18-SUM(M18:P18)))</f>
         <v/>
       </c>
-      <c r="AD18" s="4">
+      <c r="AD18" s="5">
         <f>MAX(0,R18-MAX(0,V18-SUM(M18:Q18)))</f>
         <v/>
       </c>
-      <c r="AE18" s="4">
+      <c r="AE18" s="5">
         <f>MAX(0,S18-MAX(0,V18-SUM(M18:R18)))</f>
         <v/>
       </c>
-      <c r="AF18" s="4">
+      <c r="AF18" s="5">
         <f>MAX(0,T18-MAX(0,V18-SUM(M18:S18)))</f>
         <v/>
       </c>
-      <c r="AG18" s="4">
+      <c r="AG18" s="5">
         <f>MAX(0,U18-MAX(0,V18-SUM(M18:T18)))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900238</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>HASLS22260901034</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>KMSU</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>2607S</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>202609271100</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>ECOLAB LIMITED</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>FLOOR CLEANER</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Request good and clean container</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="4" t="n">
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>INTER FRESH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>(Temp+ 2.0℃ / Vent 30% Open) Request for new container and We don't accept STAR COOL brand reefer containers.</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="4">
+      <c r="R19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="5">
         <f>SUM(M19:U19)-V19</f>
         <v/>
       </c>
-      <c r="Y19" s="4">
+      <c r="Y19" s="5">
         <f>MAX(0,M19-MAX(0,V19))</f>
         <v/>
       </c>
-      <c r="Z19" s="4">
+      <c r="Z19" s="5">
         <f>MAX(0,N19-MAX(0,V19-SUM(M19:M19)))</f>
         <v/>
       </c>
-      <c r="AA19" s="4">
+      <c r="AA19" s="5">
         <f>MAX(0,O19-MAX(0,V19-SUM(M19:N19)))</f>
         <v/>
       </c>
-      <c r="AB19" s="4">
+      <c r="AB19" s="5">
         <f>MAX(0,P19-MAX(0,V19-SUM(M19:O19)))</f>
         <v/>
       </c>
-      <c r="AC19" s="4">
+      <c r="AC19" s="5">
         <f>MAX(0,Q19-MAX(0,V19-SUM(M19:P19)))</f>
         <v/>
       </c>
-      <c r="AD19" s="4">
+      <c r="AD19" s="5">
         <f>MAX(0,R19-MAX(0,V19-SUM(M19:Q19)))</f>
         <v/>
       </c>
-      <c r="AE19" s="4">
+      <c r="AE19" s="5">
         <f>MAX(0,S19-MAX(0,V19-SUM(M19:R19)))</f>
         <v/>
       </c>
-      <c r="AF19" s="4">
+      <c r="AF19" s="5">
         <f>MAX(0,T19-MAX(0,V19-SUM(M19:S19)))</f>
         <v/>
       </c>
-      <c r="AG19" s="4">
+      <c r="AG19" s="5">
         <f>MAX(0,U19-MAX(0,V19-SUM(M19:T19)))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900358</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>SWIC</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>202609220200</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>QUAKER HOUGHTON (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>LUBRICANT</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>REQUEST CONTAINER GRADE  A OR B</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="4">
-        <f>SUM(M20:U20)-V20</f>
-        <v/>
-      </c>
-      <c r="Y20" s="4">
-        <f>MAX(0,M20-MAX(0,V20))</f>
-        <v/>
-      </c>
-      <c r="Z20" s="4">
-        <f>MAX(0,N20-MAX(0,V20-SUM(M20:M20)))</f>
-        <v/>
-      </c>
-      <c r="AA20" s="4">
-        <f>MAX(0,O20-MAX(0,V20-SUM(M20:N20)))</f>
-        <v/>
-      </c>
-      <c r="AB20" s="4">
-        <f>MAX(0,P20-MAX(0,V20-SUM(M20:O20)))</f>
-        <v/>
-      </c>
-      <c r="AC20" s="4">
-        <f>MAX(0,Q20-MAX(0,V20-SUM(M20:P20)))</f>
-        <v/>
-      </c>
-      <c r="AD20" s="4">
-        <f>MAX(0,R20-MAX(0,V20-SUM(M20:Q20)))</f>
-        <v/>
-      </c>
-      <c r="AE20" s="4">
-        <f>MAX(0,S20-MAX(0,V20-SUM(M20:R20)))</f>
-        <v/>
-      </c>
-      <c r="AF20" s="4">
-        <f>MAX(0,T20-MAX(0,V20-SUM(M20:S20)))</f>
-        <v/>
-      </c>
-      <c r="AG20" s="4">
-        <f>MAX(0,U20-MAX(0,V20-SUM(M20:T20)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900623</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>202609230100</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>20260912</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>WESTERN DIGITAL STORAGE TECHNOLOGIES (THAILAND) LTD.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>BOXBLUE BOX</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="4">
-        <f>SUM(M21:U21)-V21</f>
-        <v/>
-      </c>
-      <c r="Y21" s="4">
-        <f>MAX(0,M21-MAX(0,V21))</f>
-        <v/>
-      </c>
-      <c r="Z21" s="4">
-        <f>MAX(0,N21-MAX(0,V21-SUM(M21:M21)))</f>
-        <v/>
-      </c>
-      <c r="AA21" s="4">
-        <f>MAX(0,O21-MAX(0,V21-SUM(M21:N21)))</f>
-        <v/>
-      </c>
-      <c r="AB21" s="4">
-        <f>MAX(0,P21-MAX(0,V21-SUM(M21:O21)))</f>
-        <v/>
-      </c>
-      <c r="AC21" s="4">
-        <f>MAX(0,Q21-MAX(0,V21-SUM(M21:P21)))</f>
-        <v/>
-      </c>
-      <c r="AD21" s="4">
-        <f>MAX(0,R21-MAX(0,V21-SUM(M21:Q21)))</f>
-        <v/>
-      </c>
-      <c r="AE21" s="4">
-        <f>MAX(0,S21-MAX(0,V21-SUM(M21:R21)))</f>
-        <v/>
-      </c>
-      <c r="AF21" s="4">
-        <f>MAX(0,T21-MAX(0,V21-SUM(M21:S21)))</f>
-        <v/>
-      </c>
-      <c r="AG21" s="4">
-        <f>MAX(0,U21-MAX(0,V21-SUM(M21:T21)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260901032</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>KMSU</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>2607S</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>202609271100</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>INTER FRESH CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>(Temp +2.0℃ / Vent 30% Open) STAR COOL</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="5">
-        <f>SUM(M22:U22)-V22</f>
-        <v/>
-      </c>
-      <c r="Y22" s="5">
-        <f>MAX(0,M22-MAX(0,V22))</f>
-        <v/>
-      </c>
-      <c r="Z22" s="5">
-        <f>MAX(0,N22-MAX(0,V22-SUM(M22:M22)))</f>
-        <v/>
-      </c>
-      <c r="AA22" s="5">
-        <f>MAX(0,O22-MAX(0,V22-SUM(M22:N22)))</f>
-        <v/>
-      </c>
-      <c r="AB22" s="5">
-        <f>MAX(0,P22-MAX(0,V22-SUM(M22:O22)))</f>
-        <v/>
-      </c>
-      <c r="AC22" s="5">
-        <f>MAX(0,Q22-MAX(0,V22-SUM(M22:P22)))</f>
-        <v/>
-      </c>
-      <c r="AD22" s="5">
-        <f>MAX(0,R22-MAX(0,V22-SUM(M22:Q22)))</f>
-        <v/>
-      </c>
-      <c r="AE22" s="5">
-        <f>MAX(0,S22-MAX(0,V22-SUM(M22:R22)))</f>
-        <v/>
-      </c>
-      <c r="AF22" s="5">
-        <f>MAX(0,T22-MAX(0,V22-SUM(M22:S22)))</f>
-        <v/>
-      </c>
-      <c r="AG22" s="5">
-        <f>MAX(0,U22-MAX(0,V22-SUM(M22:T22)))</f>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6">
+        <f>SUM(M3:M19)</f>
+        <v/>
+      </c>
+      <c r="N20" s="6">
+        <f>SUM(N3:N19)</f>
+        <v/>
+      </c>
+      <c r="O20" s="6">
+        <f>SUM(O3:O19)</f>
+        <v/>
+      </c>
+      <c r="P20" s="6">
+        <f>SUM(P3:P19)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="6">
+        <f>SUM(Q3:Q19)</f>
+        <v/>
+      </c>
+      <c r="R20" s="6">
+        <f>SUM(R3:R19)</f>
+        <v/>
+      </c>
+      <c r="S20" s="6">
+        <f>SUM(S3:S19)</f>
+        <v/>
+      </c>
+      <c r="T20" s="6">
+        <f>SUM(T3:T19)</f>
+        <v/>
+      </c>
+      <c r="U20" s="6">
+        <f>SUM(U3:U19)</f>
+        <v/>
+      </c>
+      <c r="V20" s="6">
+        <f>SUM(V3:V19)</f>
+        <v/>
+      </c>
+      <c r="W20" s="6" t="n"/>
+      <c r="X20" s="6">
+        <f>SUM(X3:X19)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="6">
+        <f>SUM(Y3:Y19)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="6">
+        <f>SUM(Z3:Z19)</f>
+        <v/>
+      </c>
+      <c r="AA20" s="6">
+        <f>SUM(AA3:AA19)</f>
+        <v/>
+      </c>
+      <c r="AB20" s="6">
+        <f>SUM(AB3:AB19)</f>
+        <v/>
+      </c>
+      <c r="AC20" s="6">
+        <f>SUM(AC3:AC19)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="6">
+        <f>SUM(AD3:AD19)</f>
+        <v/>
+      </c>
+      <c r="AE20" s="6">
+        <f>SUM(AE3:AE19)</f>
+        <v/>
+      </c>
+      <c r="AF20" s="6">
+        <f>SUM(AF3:AF19)</f>
+        <v/>
+      </c>
+      <c r="AG20" s="6">
+        <f>SUM(AG3:AG19)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260901033</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>KMSU</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>2607S</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>202609271100</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>INTER FRESH CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>(Temp +2.0℃ / Vent 30% Open) Request for new container and We don't accept STAR COOL brand reefer containers.</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" s="5">
-        <f>SUM(M23:U23)-V23</f>
-        <v/>
-      </c>
-      <c r="Y23" s="5">
-        <f>MAX(0,M23-MAX(0,V23))</f>
-        <v/>
-      </c>
-      <c r="Z23" s="5">
-        <f>MAX(0,N23-MAX(0,V23-SUM(M23:M23)))</f>
-        <v/>
-      </c>
-      <c r="AA23" s="5">
-        <f>MAX(0,O23-MAX(0,V23-SUM(M23:N23)))</f>
-        <v/>
-      </c>
-      <c r="AB23" s="5">
-        <f>MAX(0,P23-MAX(0,V23-SUM(M23:O23)))</f>
-        <v/>
-      </c>
-      <c r="AC23" s="5">
-        <f>MAX(0,Q23-MAX(0,V23-SUM(M23:P23)))</f>
-        <v/>
-      </c>
-      <c r="AD23" s="5">
-        <f>MAX(0,R23-MAX(0,V23-SUM(M23:Q23)))</f>
-        <v/>
-      </c>
-      <c r="AE23" s="5">
-        <f>MAX(0,S23-MAX(0,V23-SUM(M23:R23)))</f>
-        <v/>
-      </c>
-      <c r="AF23" s="5">
-        <f>MAX(0,T23-MAX(0,V23-SUM(M23:S23)))</f>
-        <v/>
-      </c>
-      <c r="AG23" s="5">
-        <f>MAX(0,U23-MAX(0,V23-SUM(M23:T23)))</f>
-        <v/>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260901034</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>KMSU</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>2607S</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>202609271100</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>INTER FRESH CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>(Temp+ 2.0℃ / Vent 30% Open) Request for new container and We don't accept STAR COOL brand reefer containers.</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="5">
-        <f>SUM(M24:U24)-V24</f>
-        <v/>
-      </c>
-      <c r="Y24" s="5">
-        <f>MAX(0,M24-MAX(0,V24))</f>
-        <v/>
-      </c>
-      <c r="Z24" s="5">
-        <f>MAX(0,N24-MAX(0,V24-SUM(M24:M24)))</f>
-        <v/>
-      </c>
-      <c r="AA24" s="5">
-        <f>MAX(0,O24-MAX(0,V24-SUM(M24:N24)))</f>
-        <v/>
-      </c>
-      <c r="AB24" s="5">
-        <f>MAX(0,P24-MAX(0,V24-SUM(M24:O24)))</f>
-        <v/>
-      </c>
-      <c r="AC24" s="5">
-        <f>MAX(0,Q24-MAX(0,V24-SUM(M24:P24)))</f>
-        <v/>
-      </c>
-      <c r="AD24" s="5">
-        <f>MAX(0,R24-MAX(0,V24-SUM(M24:Q24)))</f>
-        <v/>
-      </c>
-      <c r="AE24" s="5">
-        <f>MAX(0,S24-MAX(0,V24-SUM(M24:R24)))</f>
-        <v/>
-      </c>
-      <c r="AF24" s="5">
-        <f>MAX(0,T24-MAX(0,V24-SUM(M24:S24)))</f>
-        <v/>
-      </c>
-      <c r="AG24" s="5">
-        <f>MAX(0,U24-MAX(0,V24-SUM(M24:T24)))</f>
-        <v/>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>HAST Logistics Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
-      <c r="M25" s="6">
-        <f>SUM(M3:M24)</f>
-        <v/>
-      </c>
-      <c r="N25" s="6">
-        <f>SUM(N3:N24)</f>
-        <v/>
-      </c>
-      <c r="O25" s="6">
-        <f>SUM(O3:O24)</f>
-        <v/>
-      </c>
-      <c r="P25" s="6">
-        <f>SUM(P3:P24)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="6">
-        <f>SUM(Q3:Q24)</f>
-        <v/>
-      </c>
-      <c r="R25" s="6">
-        <f>SUM(R3:R24)</f>
-        <v/>
-      </c>
-      <c r="S25" s="6">
-        <f>SUM(S3:S24)</f>
-        <v/>
-      </c>
-      <c r="T25" s="6">
-        <f>SUM(T3:T24)</f>
-        <v/>
-      </c>
-      <c r="U25" s="6">
-        <f>SUM(U3:U24)</f>
-        <v/>
-      </c>
-      <c r="V25" s="6">
-        <f>SUM(V3:V24)</f>
-        <v/>
-      </c>
-      <c r="W25" s="6" t="n"/>
-      <c r="X25" s="6">
-        <f>SUM(X3:X24)</f>
-        <v/>
-      </c>
-      <c r="Y25" s="6">
-        <f>SUM(Y3:Y24)</f>
-        <v/>
-      </c>
-      <c r="Z25" s="6">
-        <f>SUM(Z3:Z24)</f>
-        <v/>
-      </c>
-      <c r="AA25" s="6">
-        <f>SUM(AA3:AA24)</f>
-        <v/>
-      </c>
-      <c r="AB25" s="6">
-        <f>SUM(AB3:AB24)</f>
-        <v/>
-      </c>
-      <c r="AC25" s="6">
-        <f>SUM(AC3:AC24)</f>
-        <v/>
-      </c>
-      <c r="AD25" s="6">
-        <f>SUM(AD3:AD24)</f>
-        <v/>
-      </c>
-      <c r="AE25" s="6">
-        <f>SUM(AE3:AE24)</f>
-        <v/>
-      </c>
-      <c r="AF25" s="6">
-        <f>SUM(AF3:AF24)</f>
-        <v/>
-      </c>
-      <c r="AG25" s="6">
-        <f>SUM(AG3:AG24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="13" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="13" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>HAST Logistics Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" ht="13" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>34</v>
+      <c r="B25" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AG24"/>
+  <autoFilter ref="A2:AG19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AG1"/>
   </mergeCells>

--- a/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
+++ b/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
@@ -507,15 +507,15 @@
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1">
@@ -608,47 +608,47 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>GP22 Remaining</t>
+          <t>GP22</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>GP42 Remaining</t>
+          <t>GP42</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>GP45 Remaining</t>
+          <t>GP45</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>RE22 Remaining</t>
+          <t>RE22</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>RE45 Remaining</t>
+          <t>RE45</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>UT22 Remaining</t>
+          <t>UT22</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>UT42 Remaining</t>
+          <t>UT42</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>PC22 Remaining</t>
+          <t>PC22</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>PC42 Remaining</t>
+          <t>PC42</t>
         </is>
       </c>
     </row>

--- a/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
+++ b/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$U$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$U$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -655,25 +655,25 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260701405</t>
+          <t>HASLS22260801084</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n"/>
+          <t>202609220800</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -681,32 +681,32 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SATIEN STAINLESS STEEL PUBLIC CO., LTD.</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>STAINLESS STEEL KITCHENWARE</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>REQ CNTR : GOOD, CLEAN AND NO HOLE</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -716,7 +716,7 @@
         <v>0</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P3" s="4" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801614</t>
+          <t>HASLS22260801481</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -755,10 +755,10 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>202609211900</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n"/>
+          <t>202609211000</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -776,17 +776,17 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>INGREDION (THAILAND) CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>MODIFIED TAPIOCA STARCH (GRADE : PURITY 21T)</t>
+          <t xml:space="preserve">POLYAMIDE RESIN </t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -825,12 +825,12 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>HASLS22260801673</t>
+          <t>HASLS22260801684</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -840,10 +840,10 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>202609231400</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
+          <t>202610041300</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -861,7 +861,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>20260905</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -910,12 +910,12 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>HASLS22260801674</t>
+          <t>HASLS22260801685</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -925,10 +925,10 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>202609231400</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n"/>
+          <t>202610041300</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -946,7 +946,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>20260905</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -993,537 +993,537 @@
       </c>
     </row>
     <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260801675</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>202609231400</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801769</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>SWAL</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>202609290800</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>20260905</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>FRESH COCONUT</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5" t="n">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="5" t="n">
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260801677</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>202609250500</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802568</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>FRESH COCONUT</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="5" t="n">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>SRF INDUSTRIES (THAILAND) LIMITED (112)</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>POLYESTER FILM</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>REQ GOOD DRY AND CLEAN CONTAINER ONLY / RQST CNTR 32.5 TONS // 40'HQ</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802571</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>SRF INDUSTRIES (THAILAND) LIMITED (112)</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>POLYESTER FILM</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>REQ GOOD DRY AND CLEAN CONTAINER ONLY. / RQST CNTR 32.5 TONS // 40'HQ</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260801679</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>202609250500</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802573</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>FRESH COCONUT</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="5" t="n">
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>SRF INDUSTRIES (THAILAND) LIMITED (112)</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>POLYESTER FILM</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>REQ GOOD DRY AND CLEAN CONTAINER ONLY. / RQST CNTR 32.5 TONS // 40'HQ</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900107</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>HAB</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>202610250630</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x10 </t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>EIAM THONGCHAI INDUSTRY CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>STARCH</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>REQ : FOOD GRADE CONTAINER CLEAR &amp;DRY NO OIL NO RUSTY</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900472</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>PGPO</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>202609230830</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>TOA PERFORMANCE COATING CORPORATION CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>ABRASIVE PAPER / H.S CODE ; 6805.20</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260801681</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>202609250500</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>FRESH COCONUT</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260801684</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>SWAT</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>202610041300</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>FRESH COCONUT</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260801685</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>SWAT</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>202610041300</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>FRESH COCONUT</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="5" t="n">
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900107</t>
+          <t>HASLS22260900478</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>202610250630</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n"/>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1531,42 +1531,42 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x10 </t>
+          <t xml:space="preserve">40Hx5 </t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>EIAM THONGCHAI INDUSTRY CO.,LTD.</t>
+          <t>MAXXIS INTERNATIONAL (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>STARCH</t>
+          <t>NEW TIRE</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>REQ : FOOD GRADE CONTAINER CLEAR &amp;DRY NO OIL NO RUSTY</t>
+          <t>REQUEST GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0</v>
@@ -1590,25 +1590,25 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900237</t>
+          <t>HASLS22260900529</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n"/>
+          <t>202609270600</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1626,22 +1626,22 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>ECOLAB LIMITED</t>
+          <t>SIAM TOHCELLO COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>QUATERNARY AMMONIUM COMPOUND DRM</t>
+          <t>PLASTIC WRAP FOR FOOD</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>APPROVAL BY Mr.LEE MINHA DD.07/09/2026 (CLS 8 / UN 2920) Request good and clean container</t>
+          <t>REQ FOOD GRADE CONTAINER</t>
         </is>
       </c>
       <c r="M14" s="4" t="n">
@@ -1673,112 +1673,112 @@
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900238</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>2607S</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>HASLS22260900750</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>ECOLAB LIMITED</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>FLOOR CLEANER</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>Request good and clean container</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="4" t="n">
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>GOLDEN SEA FROZEN FOODS CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>FROZEN FISH</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>RF45REx1 (Temp -18.0℃ / Vent Close)</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="4" t="n">
+      <c r="R15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900623</t>
+          <t>HASLS22260900926</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>202609231400</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n"/>
+          <t>202609290800</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>20260912</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>WESTERN DIGITAL STORAGE TECHNOLOGIES (THAILAND) LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>BOXBLUE BOX</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M16" s="4" t="n">
@@ -1843,359 +1843,615 @@
       </c>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260900952</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>SKOR</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900927</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>SWAL</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>202609290800</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x2 </t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900928</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>SWAL</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>202609290800</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x7 </t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260901091</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>HAB</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>2611N</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>202609271030</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>202609270600</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>DYNAMIC TECHNOLOGY MANUFACTURING (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>PRINTED CIRCUIT BOARD</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>good and clean container condition (Container grade A)</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>HASLS22260901468</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>KMSU</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>2607S</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>202609271100</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>20260916</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>FRESH LONGAN</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 15% Open)</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5" t="n">
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>INTER FRESH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>(Temp +2.0℃ / Vent 30% Open)
+Request for new container and We don't accept STAR COOL brand reefer containers.</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="R17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260901033</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>KMSU</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>2607S</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>202609271100</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="R20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260901566</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>SWAL</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>202609290800</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>INTER FRESH CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>(Temp +2.0℃ / Vent 30% Open) Request for new container and We don't accept STAR COOL brand reefer containers.</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>HASLS22260901034</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>KMSU</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>2607S</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>202609271100</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x7 </t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260901568</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>SWAL</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>202609290800</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>INTER FRESH CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>(Temp+ 2.0℃ / Vent 30% Open) Request for new container and We don't accept STAR COOL brand reefer containers.</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x3 </t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
-      <c r="M20" s="6">
-        <f>SUM(M3:M19)</f>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6">
+        <f>SUM(M3:M22)</f>
         <v/>
       </c>
-      <c r="N20" s="6">
-        <f>SUM(N3:N19)</f>
+      <c r="N23" s="6">
+        <f>SUM(N3:N22)</f>
         <v/>
       </c>
-      <c r="O20" s="6">
-        <f>SUM(O3:O19)</f>
+      <c r="O23" s="6">
+        <f>SUM(O3:O22)</f>
         <v/>
       </c>
-      <c r="P20" s="6">
-        <f>SUM(P3:P19)</f>
+      <c r="P23" s="6">
+        <f>SUM(P3:P22)</f>
         <v/>
       </c>
-      <c r="Q20" s="6">
-        <f>SUM(Q3:Q19)</f>
+      <c r="Q23" s="6">
+        <f>SUM(Q3:Q22)</f>
         <v/>
       </c>
-      <c r="R20" s="6">
-        <f>SUM(R3:R19)</f>
+      <c r="R23" s="6">
+        <f>SUM(R3:R22)</f>
         <v/>
       </c>
-      <c r="S20" s="6">
-        <f>SUM(S3:S19)</f>
+      <c r="S23" s="6">
+        <f>SUM(S3:S22)</f>
         <v/>
       </c>
-      <c r="T20" s="6">
-        <f>SUM(T3:T19)</f>
+      <c r="T23" s="6">
+        <f>SUM(T3:T22)</f>
         <v/>
       </c>
-      <c r="U20" s="6">
-        <f>SUM(U3:U19)</f>
+      <c r="U23" s="6">
+        <f>SUM(U3:U22)</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Pickup Name</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Number of Records</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Total Balance</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="13" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="27" ht="13" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>HAST Logistics Co.,Ltd.</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="B27" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>29</v>
+      <c r="B28" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:U19"/>
+  <autoFilter ref="A2:U22"/>
   <mergeCells count="1">
     <mergeCell ref="A1:U1"/>
   </mergeCells>

--- a/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
+++ b/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
@@ -495,27 +495,27 @@
   <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="5" customWidth="1" min="19" max="19"/>
+    <col width="5" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1">

--- a/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
+++ b/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -615,22 +615,22 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801436</t>
+          <t>HASLS22260900107</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KUS</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202610152100</t>
+          <t>202610280600</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -641,36 +641,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>JPSBS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x10 </t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>TONG THAI RUBBER CO., LTD.</t>
+          <t>EIAM THONGCHAI INDUSTRY CO.,LTD.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>NATURAL RUBBER</t>
+          <t>STARCH</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQ : FOOD GRADE CONTAINER CLEAR &amp;DRY NO OIL NO RUSTY</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -700,12 +700,12 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900107</t>
+          <t>HASLS22260900464</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610252200</t>
+          <t>202610271500</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -726,42 +726,42 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x10 </t>
+          <t xml:space="preserve">40Hx8 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>EIAM THONGCHAI INDUSTRY CO.,LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>STARCH</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>REQ : FOOD GRADE CONTAINER CLEAR &amp;DRY NO OIL NO RUSTY</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>0</v>
@@ -785,22 +785,22 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900413</t>
+          <t>HASLS22260901109</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KMSU</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610312130</t>
+          <t>202610220200</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -811,32 +811,32 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>MAJESTY HOLDINGS (ASIA) CO.,LTD.</t>
+          <t>SENNICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>SIRANTOX 6PPD(4020)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>goog and clean</t>
+          <t>GOOD DRY AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>0</v>
@@ -870,22 +870,22 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900462</t>
+          <t>HASLS22260901805</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202610152200</t>
+          <t>202610220430</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -896,32 +896,32 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx8 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>CAM PLAS (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>PLASTIC</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>0</v>
@@ -953,87 +953,87 @@
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901330</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SWBT</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>202610161300</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22260901941</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>202610300000</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x12 </t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20261005</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CTNR</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="2" t="n">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>POSTMAN (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>RF45REx1 (Temp +2.0℃ / Vent 15% Open)</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>202610211300</t>
+          <t>202610231500</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
@@ -1125,22 +1125,22 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>HASLS22260902288</t>
+          <t>HASLS22260901967</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>202610210800</t>
+          <t>202610231500</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
@@ -1151,120 +1151,120 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>20261010</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>POSTMAN (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>RF45REx1 (Temp +2.0℃ / Vent 15% Open)</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22260902288</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>202610220430</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>20261009</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>INTER FRESH CO., LTD.</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>(Temp +2.0℃ / Vent 30% Open) 
 Request for new container and We don't accept STAR COOL brand reefer containers.</t>
         </is>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>HASLS22260902289</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>202610210800</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>INTER FRESH CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>(Temp +2.0℃ / Vent 30% Open) Request for new container and We don't accept STAR COOL brand reefer containers.</t>
-        </is>
-      </c>
       <c r="M9" s="3" t="n">
         <v>0</v>
       </c>
@@ -1296,22 +1296,22 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>HASLS22261000788</t>
+          <t>HASLS22260902289</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>202610150200</t>
+          <t>202610220430</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20RFx1 </t>
+          <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>PROWELL INTERNATIONAL EXPRESS CO., LTD.</t>
+          <t>INTER FRESH CO., LTD.</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>FRESH POMELO</t>
+          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>(Temp +10.0℃ / Vent 30% Open)ON DECK, REQUEST NEW AND CLEAN CONTAINER CARRIER BRAND (NOT OVER 3 YEAR)</t>
+          <t>(Temp +2.0℃ / Vent 30% Open) Request for new container and We don't accept STAR COOL brand reefer containers.</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
@@ -1360,11 +1360,11 @@
         <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" s="3" t="n">
         <v>0</v>
       </c>
@@ -1379,104 +1379,2152 @@
       </c>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22260902290</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>202610251100</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>INTER FRESH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0℃ / Vent 30% Open)
+Request for new container and We don't accept STAR COOL brand reefer containers.</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22260902291</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>202610251100</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>INTER FRESH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0℃ / Vent 30% Open)Request for new container and We don't accept STAR COOL brand reefer containers.</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000067</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>202610220430</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0 / Vent 15%) 
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000077</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SWAL</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202610220200</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>ADVANCE ASIA FIBER CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HARDBOARD  </t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000093</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>202610220430</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0 / Vent 15%) 
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000094</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>202610220430</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0 / Vent 15%) 
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000095</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>202610220430</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0 / Vent 15%) 
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000096</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>202610220430</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0 / Vent 15%) 
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000233</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>202610220430</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>20261010</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0℃ / Vent 10% Open)</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000235</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>202610220430</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>20261010</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0 / Vent 10% Open)</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000236</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>202610220430</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>20261010</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>BE 1ST ALLIANCE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0℃ / Vent 10% Open)</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000237</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>202610251100</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>RF45REx1 (RF45REx1 (Temp 2.0℃ / Vent 10% Open)</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000238</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>202610251100</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0 / Vent 10% Open)</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000239</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>202610251100</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>OK FRESH FRUITS (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0℃ / Vent 10% Open)</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000254</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>202610220430</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>ZIKER CO., LTD</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>STEEL SHOT</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000446</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>202610251100</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN 
+TEMP +2 VENT 15%
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="13" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000590</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>YSVY</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>202610220430</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>THAI WAH PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>BIOPLASTIC COMPOUND ROSECO CSE-X1</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000628</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>202610240200</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="13" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000629</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>202610240200</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x6 </t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="13" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000639</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>202610240200</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x6 </t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000640</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>202610240200</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x6 </t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000667</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>202610271500</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x4 </t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000673</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>202610240200</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261001019</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>202610240200</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4">
-        <f>SUM(M2:M10)</f>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4">
+        <f>SUM(M2:M34)</f>
         <v/>
       </c>
-      <c r="N11" s="4">
-        <f>SUM(N2:N10)</f>
+      <c r="N35" s="4">
+        <f>SUM(N2:N34)</f>
         <v/>
       </c>
-      <c r="O11" s="4">
-        <f>SUM(O2:O10)</f>
+      <c r="O35" s="4">
+        <f>SUM(O2:O34)</f>
         <v/>
       </c>
-      <c r="P11" s="4">
-        <f>SUM(P2:P10)</f>
+      <c r="P35" s="4">
+        <f>SUM(P2:P34)</f>
         <v/>
       </c>
-      <c r="Q11" s="4">
-        <f>SUM(Q2:Q10)</f>
+      <c r="Q35" s="4">
+        <f>SUM(Q2:Q34)</f>
         <v/>
       </c>
-      <c r="R11" s="4">
-        <f>SUM(R2:R10)</f>
+      <c r="R35" s="4">
+        <f>SUM(R2:R34)</f>
         <v/>
       </c>
-      <c r="S11" s="4">
-        <f>SUM(S2:S10)</f>
+      <c r="S35" s="4">
+        <f>SUM(S2:S34)</f>
         <v/>
       </c>
-      <c r="T11" s="4">
-        <f>SUM(T2:T10)</f>
+      <c r="T35" s="4">
+        <f>SUM(T2:T34)</f>
         <v/>
       </c>
-      <c r="U11" s="4">
-        <f>SUM(U2:U10)</f>
+      <c r="U35" s="4">
+        <f>SUM(U2:U34)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Pickup Name</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Number of Records</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Total Balance</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>HAST Logistics Co.,Ltd.</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="B39" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" ht="13" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>35</v>
+      <c r="B40" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U10"/>
+  <autoFilter ref="A1:U34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
+++ b/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -615,22 +615,22 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901938</t>
+          <t>HASLS22260901941</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SWVG</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202610290800</t>
+          <t>202611020200</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -651,7 +651,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -700,22 +700,22 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901941</t>
+          <t>HASLS22260902293</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>KMSU</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202611011500</t>
+          <t>202611012100</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -736,22 +736,23 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
+          <t>INTER FRESH CO., LTD.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>FRESH LONGAN</t>
+          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 15% Open)</t>
+          <t>(Temp +2.0℃ / Vent 30% Open) 
+Request for new container and We don't accept STAR COOL brand reefer containers.</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
@@ -785,7 +786,7 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902293</t>
+          <t>HASLS22260902294</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -871,12 +872,12 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902294</t>
+          <t>HASLS22261000237</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KMSU</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -886,7 +887,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202611012100</t>
+          <t>202610290200</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -907,23 +908,22 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>INTER FRESH CO., LTD.</t>
+          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
+          <t>FRESH  LONGAN / +2'C VENT 15%</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>(Temp +2.0℃ / Vent 30% Open) 
-Request for new container and We don't accept STAR COOL brand reefer containers.</t>
+          <t>(Temp 2.0℃ / Vent 15% Open)</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
@@ -955,354 +955,354 @@
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>HASLS22260902643</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>HAB</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>202610282300</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000238</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>202610290200</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>GROHE SIAM LIMITED</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>SANITARY WARE</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Request dry, Strong floor and good container condition</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="n">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>(Temp +2.0 / Vent 15% Open)</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3" t="n">
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>HASLS22260902847</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>KMBK</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>202610262300</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000239</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>202610290200</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx4 </t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CTNR</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3" t="n">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>OK FRESH FRUITS (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>(Temp +2.0℃ / Vent 15% Open)</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>HASLS22261000128</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000240</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>KMSU</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2608S</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>202610290200</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>202611012100</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x4 </t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>20261019</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>PTT OIL AND RETAIL BUSINESS PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Building / Equipment</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3" t="n">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>(Temp +2.0 / Vent 10% Open)</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>HASLS22261000195</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000241</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>KMSU</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>2608S</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>202610290200</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>202611012100</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>PACIFIC SUGAR CORPORATION LIMITED</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>REFINED SUGAR</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Food grade</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>(Temp +2.0 / Vent 10% Open)</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="3" t="n">
+      <c r="R9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000237</t>
+          <t>HASLS22261000242</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>KMSU</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610290200</t>
+          <t>202611012100</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
+          <t>OK FRESH FRUITS (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>(Temp 2.0℃ / Vent 15% Open)</t>
+          <t>(Temp +2.0 / Vent 10% Open)</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
@@ -1382,7 +1382,7 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000239</t>
+          <t>HASLS22261000443</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1418,22 +1418,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>OK FRESH FRUITS (THAILAND) CO.,LTD.</t>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>(Temp +2.0℃ / Vent 15% Open)</t>
+          <t>FRESH LONGAN 
+TEMP +2 VENT 15%
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
@@ -1467,12 +1469,12 @@
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000240</t>
+          <t>HASLS22261000446</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>KMSU</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1482,7 +1484,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>202611012100</t>
+          <t>202610290200</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1503,22 +1505,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>(Temp +2.0 / Vent 10% Open)</t>
+          <t>FRESH LONGAN 
+TEMP +2 VENT 15%
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
@@ -1552,12 +1556,12 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000241</t>
+          <t>HASLS22261000447</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>KMSU</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1567,7 +1571,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>202611012100</t>
+          <t>202610290200</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1588,22 +1592,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
+          <t>PROGRESS SHIPPING - TRANSPORT CO., LTD.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>(Temp +2.0 / Vent 10% Open)</t>
+          <t>FRESH LONGAN 
+TEMP +2 VENT 15%
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
@@ -1637,12 +1643,12 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000242</t>
+          <t>HASLS22261000450</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>KMSU</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1652,7 +1658,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>202611012100</t>
+          <t>202610290200</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1673,22 +1679,24 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>OK FRESH FRUITS (THAILAND) CO.,LTD.</t>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>(Temp +2.0 / Vent 10% Open)</t>
+          <t>FRESH LONGAN 
+TEMP +2 VENT 15%
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
@@ -1722,7 +1730,7 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000443</t>
+          <t>HASLS22261000451</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1807,285 +1815,280 @@
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000446</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>202610290200</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000676</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>DJCF</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>0153N</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>202611031700</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>FRESH LONGAN 
-TEMP +2 VENT 15%
-REQUEST CONTAINER UPSIZE 34-35 TONS</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="2" t="n">
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx8 </t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>REFRIGERATOR</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>*No containers with cut and patch marks inside*
+GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000447</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>202610290200</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261001082</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>KXM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>202611130200</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>PROGRESS SHIPPING - TRANSPORT CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>FRESH LONGAN 
-TEMP +2 VENT 15%
-REQUEST CONTAINER UPSIZE 34-35 TONS</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="2" t="n">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x5 </t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>NIKKEI MC ALUMINUM (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALUMINUM ALLOY INGOT </t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000450</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>202610290200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261001119</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>SWBT</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2618N</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>202611082000</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>FRESH LONGAN 
-TEMP +2 VENT 15%
-REQUEST CONTAINER UPSIZE 34-35 TONS</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="2" t="n">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>SRI TRANG GLOVES (THAILAND) PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>LATEX GLOVES</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="2" t="n">
+      <c r="N18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000451</t>
+          <t>HASLS22261001347</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>202610290200</t>
+          <t>202610280700</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -2096,7 +2099,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>RUVVO</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2106,24 +2109,22 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
+          <t>EXOTIC FOOD PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
+          <t>General Foodstuff</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>FRESH LONGAN 
-TEMP +2 VENT 15%
-REQUEST CONTAINER UPSIZE 34-35 TONS</t>
+          <t>(TEMP : +18.0'C / VENT CLOSE)</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
@@ -2155,870 +2156,104 @@
       </c>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>HASLS22261000533</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>202610290200</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>THAI MFC CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>MELAMINE MOULDING COMPOUND</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>No damaged and clean container request</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>HASLS22261000640</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>202610251730</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x6 </t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CTNR</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>HASLS22261000676</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>DJCF</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>0153N</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>202611030400</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx8 </t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>REFRIGERATOR</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>*No containers with cut and patch marks inside*
-GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>0</v>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4">
+        <f>SUM(M2:M19)</f>
+        <v/>
+      </c>
+      <c r="N20" s="4">
+        <f>SUM(N2:N19)</f>
+        <v/>
+      </c>
+      <c r="O20" s="4">
+        <f>SUM(O2:O19)</f>
+        <v/>
+      </c>
+      <c r="P20" s="4">
+        <f>SUM(P2:P19)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="4">
+        <f>SUM(Q2:Q19)</f>
+        <v/>
+      </c>
+      <c r="R20" s="4">
+        <f>SUM(R2:R19)</f>
+        <v/>
+      </c>
+      <c r="S20" s="4">
+        <f>SUM(S2:S19)</f>
+        <v/>
+      </c>
+      <c r="T20" s="4">
+        <f>SUM(T2:T19)</f>
+        <v/>
+      </c>
+      <c r="U20" s="4">
+        <f>SUM(U2:U19)</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>HASLS22261001082</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>KXM</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>202611090200</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x5 </t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>NIKKEI MC ALUMINUM (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALUMINUM ALLOY INGOT </t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>0</v>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>HASLS22261001119</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>SWBT</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>202611071800</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>SRI TRANG GLOVES (THAILAND) PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>LATEX GLOVES</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>0</v>
+          <t>HAST Logistics Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>HASLS22261001156</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>KMGY</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>202610241900</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx9 </t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>KURARAY GC ADVANCED MATERIALS CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>GENESTAR</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>Good dry and clean container</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="13" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>HASLS22261001232</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>202610290200</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x2 </t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>THAI MFC CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>MELAMINE MOULDING COMPOUND</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>No damaged and clean container request</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="13" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001347</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>202610280700</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>RUVVO</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>EXOTIC FOOD PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>General Foodstuff</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>(TEMP : +18.0'C / VENT CLOSE)</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="13" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001401</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>202610280700</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>GOLDEN SEA FROZEN FOODS CO.,LTD</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>FROZEN FISH</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>(Temp -18.0℃ / Vent Close)</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="13" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="n"/>
-      <c r="L29" s="4" t="n"/>
-      <c r="M29" s="4">
-        <f>SUM(M2:M28)</f>
-        <v/>
-      </c>
-      <c r="N29" s="4">
-        <f>SUM(N2:N28)</f>
-        <v/>
-      </c>
-      <c r="O29" s="4">
-        <f>SUM(O2:O28)</f>
-        <v/>
-      </c>
-      <c r="P29" s="4">
-        <f>SUM(P2:P28)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="4">
-        <f>SUM(Q2:Q28)</f>
-        <v/>
-      </c>
-      <c r="R29" s="4">
-        <f>SUM(R2:R28)</f>
-        <v/>
-      </c>
-      <c r="S29" s="4">
-        <f>SUM(S2:S28)</f>
-        <v/>
-      </c>
-      <c r="T29" s="4">
-        <f>SUM(T2:T28)</f>
-        <v/>
-      </c>
-      <c r="U29" s="4">
-        <f>SUM(U2:U28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>HAST Logistics Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>44</v>
+      <c r="B25" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U28"/>
+  <autoFilter ref="A1:U19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
+++ b/output/bkg pending - HAST Logistics Co.,Ltd.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -102,10 +102,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -615,22 +615,22 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901941</t>
+          <t>HASLS22260900469</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202611020200</t>
+          <t>202611082100</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -641,36 +641,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">R40Hx1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>POSTMAN (THAILAND) CO.,LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>FRESH LONGAN</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>RF45REx1 (Temp +2.0℃ / Vent 15% Open)</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -700,22 +700,22 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902293</t>
+          <t>HASLS22260900470</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KMSU</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>0153N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202611012100</t>
+          <t>202611032200</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -726,37 +726,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">R40Hx1 </t>
+          <t xml:space="preserve">20'x9 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>INTER FRESH CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>(Temp +2.0℃ / Vent 30% Open) 
-Request for new container and We don't accept STAR COOL brand reefer containers.</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
@@ -768,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="2" t="n">
         <v>0</v>
@@ -786,22 +785,22 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902294</t>
+          <t>HASLS22260900471</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KMSU</t>
+          <t>KUS</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202611012100</t>
+          <t>202611070000</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -812,162 +811,161 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">20'x20 </t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="13" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22260901941</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>202611020200</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>INTER FRESH CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FRESH LONGAN (TEMP +2.0 / VENT 30%) </t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>(Temp +2.0℃ / Vent 30% Open) 
-Request for new container and We don't accept STAR COOL brand reefer containers.</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="n">
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>POSTMAN (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>RF45REx1 (Temp +2.0℃ / Vent 15% Open)</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000237</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>202610290200</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20261012</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>FRESH  LONGAN / +2'C VENT 15%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>(Temp 2.0℃ / Vent 15% Open)</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2" t="n">
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000238</t>
+          <t>HASLS22260902643</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -983,32 +981,32 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">R40Hx1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
+          <t>GROHE SIAM LIMITED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+          <t>SANITARY WARE</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>(Temp +2.0 / Vent 15% Open)</t>
+          <t>Request dry, Strong floor and good container condition</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
@@ -1018,13 +1016,13 @@
         <v>0</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="2" t="n">
         <v>0</v>
@@ -1042,22 +1040,22 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000239</t>
+          <t>HASLS22260902842</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>KUS</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202610290200</t>
+          <t>202611070000</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1068,36 +1066,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">R40Hx1 </t>
+          <t xml:space="preserve">20'x9 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>OK FRESH FRUITS (THAILAND) CO.,LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>FRESH  LONGAN / +2'C VENT 15%</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>(Temp +2.0℃ / Vent 15% Open)</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1109,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>0</v>
@@ -1127,22 +1125,22 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000240</t>
+          <t>HASLS22261000214</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>KMSU</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>0153N</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202611012100</t>
+          <t>202611032200</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1153,686 +1151,686 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x5 </t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000237</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>202610290200</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>FRESH  LONGAN / +2'C VENT 15%</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>(Temp +2.0 / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2" t="n">
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>(Temp 2.0℃ / Vent 15% Open)</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000241</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>KMSU</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="R9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000238</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>2608S</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>202611012100</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>202610290200</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>SUCCESS IMPORT &amp; EXPORT CO., LTD.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>FRESH  LONGAN / +2'C VENT 15%</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>(Temp +2.0 / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2" t="n">
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0 / Vent 15% Open)</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000242</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>KMSU</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="R10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000443</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>2608S</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>202611012100</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>202610290200</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>OK FRESH FRUITS (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>FRESH  LONGAN / +2'C VENT 15%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>(Temp +2.0 / Vent 10% Open)</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000443</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>NSSJ</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>202610290200</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R40Hx1 </t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>20261016</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>FRESH LONGAN 
 TEMP +2 VENT 15%
 REQUEST CONTAINER UPSIZE 34-35 TONS</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="2" t="n">
+      <c r="M11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="2" t="n">
+      <c r="R11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>HASLS22261000446</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>NSSJ</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>2608S</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>202610290200</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>20261015</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>FRESH LONGAN 
 TEMP +2 VENT 15%
 REQUEST CONTAINER UPSIZE 34-35 TONS</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="2" t="n">
+      <c r="M12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="2" t="n">
+      <c r="R12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>HASLS22261000447</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>NSSJ</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>2608S</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>202610290200</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>20261016</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>PROGRESS SHIPPING - TRANSPORT CO., LTD.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>FRESH LONGAN 
 TEMP +2 VENT 15%
 REQUEST CONTAINER UPSIZE 34-35 TONS</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="2" t="n">
+      <c r="M13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="2" t="n">
+      <c r="R13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>HASLS22261000450</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>NSSJ</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>2608S</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>202610290200</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>20261016</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>FRESH LONGAN 
 TEMP +2 VENT 15%
 REQUEST CONTAINER UPSIZE 34-35 TONS</t>
         </is>
       </c>
-      <c r="M14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="2" t="n">
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="2" t="n">
+      <c r="R14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>HASLS22261000451</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>NSSJ</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>2608S</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>202610290200</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>20261016</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>FRESH LONGAN 
 TEMP +2 VENT 15%
 REQUEST CONTAINER UPSIZE 34-35 TONS</t>
         </is>
       </c>
-      <c r="M15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="2" t="n">
+      <c r="M15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="2" t="n">
+      <c r="R15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>HASLS22261000676</t>
+          <t>HASLS22261000454</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>KMSU</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>0153N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>202611031700</t>
+          <t>202611012100</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr"/>
@@ -1843,417 +1841,1277 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN 
+TEMP +2 VENT 15%
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000455</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>KMSU</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>202611012100</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN 
+TEMP +2 VENT 15%
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000456</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>KMSU</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>202611012100</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN 
+TEMP +2 VENT 15%
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000457</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>KMSU</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>202611012100</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN 
+TEMP +2 VENT 15%
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261000458</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>KMSU</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>202611012100</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R40Hx1 </t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>FRUIT PARADISE INTERNATIONAL TRADE CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN (TEMP +2 VENT 15%)</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>FRESH LONGAN 
+TEMP +2 VENT 15%
+REQUEST CONTAINER UPSIZE 34-35 TONS</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000676</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>DJCF</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0153N</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>202611032200</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>KRPTK</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx8 </t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>20261019</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>REFRIGERATOR</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>*No containers with cut and patch marks inside*
 GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
         </is>
       </c>
-      <c r="M16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="3" t="n">
+      <c r="M21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="P21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261001035</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>DJCF</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0153N</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>202611032200</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x6 </t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>HASLS22261001082</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>KXM</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>2609S</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>202611130200</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>20261019</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>NIKKEI MC ALUMINUM (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ALUMINUM ALLOY INGOT </t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="N23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>HASLS22261001119</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>SWBT</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>2618N</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>202611082000</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>KRINC</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>20261019</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>SRI TRANG GLOVES (THAILAND) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>LATEX GLOVES</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001347</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>202610280700</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="N24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261001736</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>202611082100</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>RUVVO</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x6 </t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261001737</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>202611082100</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x3 </t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="13" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261001738</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>202611082100</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261001739</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>202611082100</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x2 </t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="13" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22261001860</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>SWVG</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>202610291300</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">R40Hx1 </t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>EXOTIC FOOD PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>General Foodstuff</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>(TEMP : +18.0'C / VENT CLOSE)</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="2" t="n">
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>HI HAPPY TRADING CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>FRESH YOUNG COCONUT</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>(Temp +2.0℃ / Vent 15% Open)</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="R29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="13" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4">
-        <f>SUM(M2:M19)</f>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4">
+        <f>SUM(M2:M29)</f>
         <v/>
       </c>
-      <c r="N20" s="4">
-        <f>SUM(N2:N19)</f>
+      <c r="N30" s="4">
+        <f>SUM(N2:N29)</f>
         <v/>
       </c>
-      <c r="O20" s="4">
-        <f>SUM(O2:O19)</f>
+      <c r="O30" s="4">
+        <f>SUM(O2:O29)</f>
         <v/>
       </c>
-      <c r="P20" s="4">
-        <f>SUM(P2:P19)</f>
+      <c r="P30" s="4">
+        <f>SUM(P2:P29)</f>
         <v/>
       </c>
-      <c r="Q20" s="4">
-        <f>SUM(Q2:Q19)</f>
+      <c r="Q30" s="4">
+        <f>SUM(Q2:Q29)</f>
         <v/>
       </c>
-      <c r="R20" s="4">
-        <f>SUM(R2:R19)</f>
+      <c r="R30" s="4">
+        <f>SUM(R2:R29)</f>
         <v/>
       </c>
-      <c r="S20" s="4">
-        <f>SUM(S2:S19)</f>
+      <c r="S30" s="4">
+        <f>SUM(S2:S29)</f>
         <v/>
       </c>
-      <c r="T20" s="4">
-        <f>SUM(T2:T19)</f>
+      <c r="T30" s="4">
+        <f>SUM(T2:T29)</f>
         <v/>
       </c>
-      <c r="U20" s="4">
-        <f>SUM(U2:U19)</f>
+      <c r="U30" s="4">
+        <f>SUM(U2:U29)</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Pickup Name</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Number of Records</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Total Balance</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="13" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>HAST Logistics Co.,Ltd.</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="B34" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>23</v>
+      <c r="B35" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U19"/>
+  <autoFilter ref="A1:U29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>